--- a/LED Power Board/Project Outputs/BOM/Active BOM-ActiveBOM(Production).xlsx
+++ b/LED Power Board/Project Outputs/BOM/Active BOM-ActiveBOM(Production).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil\Documents\code\dmx_interface_dev_board_v2\LED Power Board\Project Outputs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{779ED91A-28E4-4AF7-892E-12CFA385073F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E83A9978-89CA-4658-BF57-96850D4B760E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="2580" windowWidth="31570" windowHeight="17480" xr2:uid="{350C3374-8633-4E41-A2B9-70B9EC2018DD}"/>
+    <workbookView xWindow="2120" yWindow="2580" windowWidth="31570" windowHeight="17480" xr2:uid="{30406514-EA8E-49D5-B937-9EE9712259BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Active BOM-ActiveBOM(Production" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>JLCPN</t>
   </si>
@@ -99,6 +99,21 @@
   </si>
   <si>
     <t>581-REH1020471M050K</t>
+  </si>
+  <si>
+    <t>5.0SMDJ5.0A</t>
+  </si>
+  <si>
+    <t>5V Unidirectional 5kW TVS Diode, 9.2V Vwm, 6.4V Vbr, SMC(DO-214AB), SMD</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SMDJ_DO-214AB</t>
+  </si>
+  <si>
+    <t>CMP-004-00056-1</t>
   </si>
   <si>
     <t>3544-2</t>
@@ -614,8 +629,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8202100-22FD-421B-B013-04569AAA3AFD}">
-  <dimension ref="A1:K8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9BBDEE-6568-47E1-A910-C19F97DF769F}">
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.81640625" customWidth="1"/>
@@ -709,180 +724,205 @@
         <v>23</v>
       </c>
       <c r="G3" s="1">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G4" s="1">
         <v>8</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>8</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="1">
-        <v>4</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="1">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>58</v>
+      <c r="K9" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
